--- a/contributors/latest/contributors.xlsx
+++ b/contributors/latest/contributors.xlsx
@@ -112,12 +112,12 @@
     <t>is_contact</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>is_principal_investigator</t>
   </si>
   <si>
@@ -145,7 +145,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2023-11-07T20:05:24-08:00</t>
+    <t>2026-10-21T13:28:14-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -231,17 +231,17 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" style="2" width="10.41796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" style="3" width="10.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" style="4" width="21.609375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" style="5" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" style="6" width="9.484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" style="7" width="5.54296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" style="8" width="5.84765625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" style="9" width="9.94921875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" style="10" width="22.5859375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" style="11" width="11.05078125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" style="12" width="19.61328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" style="2" width="8.98828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" style="3" width="8.6328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" style="4" width="18.640625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" style="5" width="11.3125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" style="6" width="8.18359375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" style="7" width="4.78125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" style="8" width="5.046875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" style="9" width="8.58203125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" style="10" width="19.48046875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" style="11" width="9.53125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" style="12" width="16.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -280,7 +280,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="12">
         <v>13</v>
       </c>
     </row>
@@ -308,12 +308,12 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>9</v>
       </c>
     </row>
@@ -328,12 +328,12 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>9</v>
       </c>
     </row>
@@ -348,12 +348,12 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>9</v>
       </c>
     </row>
@@ -367,37 +367,37 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.1875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.9921875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="80.8828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.20703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.65234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.1484375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="69.76953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>21</v>
       </c>
     </row>
